--- a/results/metrics_modelling2.xlsx
+++ b/results/metrics_modelling2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,19 +487,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8686868686868686</v>
+        <v>0.845360824742268</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7997685185185186</v>
+        <v>0.7789351851851851</v>
       </c>
     </row>
     <row r="3">
@@ -519,19 +519,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="E3" t="n">
         <v>0.8571428571428572</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.84</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7465277777777777</v>
+        <v>0.7893518518518519</v>
       </c>
     </row>
     <row r="4">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8686868686868686</v>
+        <v>0.845360824742268</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7997685185185186</v>
+        <v>0.7789351851851851</v>
       </c>
     </row>
     <row r="5">
@@ -586,16 +586,16 @@
         <v>0.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.854368932038835</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9375</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7465277777777777</v>
+        <v>0.7546296296296295</v>
       </c>
     </row>
     <row r="6">
@@ -615,19 +615,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6266666666666667</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8659793814432989</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6435185185185186</v>
+        <v>0.8078703703703703</v>
       </c>
     </row>
     <row r="7">
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8440366972477064</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.7361111111111112</v>
       </c>
     </row>
     <row r="8">
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.6266666666666667</v>
+        <v>0.84</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6435185185185186</v>
+        <v>0.8425925925925926</v>
       </c>
     </row>
     <row r="9">
@@ -714,16 +714,16 @@
         <v>0.7733333333333333</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8440366972477064</v>
+        <v>0.8349514563106797</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.7818181818181819</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.7256944444444445</v>
       </c>
     </row>
     <row r="10">
@@ -743,19 +743,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8282828282828283</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="F10" t="n">
-        <v>0.803921568627451</v>
+        <v>0.851063829787234</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7418981481481481</v>
+        <v>0.7870370370370371</v>
       </c>
     </row>
     <row r="11">
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8349514563106797</v>
+        <v>0.8659793814432989</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7818181818181819</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7256944444444445</v>
+        <v>0.8078703703703703</v>
       </c>
     </row>
     <row r="12">
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8282828282828283</v>
+        <v>0.8602150537634408</v>
       </c>
       <c r="F12" t="n">
-        <v>0.803921568627451</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7418981481481481</v>
+        <v>0.8240740740740742</v>
       </c>
     </row>
     <row r="13">
@@ -839,19 +839,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8349514563106797</v>
+        <v>0.8686868686868686</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7818181818181819</v>
+        <v>0.8431372549019608</v>
       </c>
       <c r="G13" t="n">
         <v>0.8958333333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7256944444444445</v>
+        <v>0.7997685185185186</v>
       </c>
     </row>
     <row r="14">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.8</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6938775510204082</v>
+        <v>0.7659574468085106</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G18" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8159090909090909</v>
+        <v>0.8681818181818182</v>
       </c>
     </row>
     <row r="19">
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.88</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7368421052631577</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8136363636363635</v>
+        <v>0.8545454545454545</v>
       </c>
     </row>
     <row r="20">
@@ -1063,19 +1063,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6938775510204082</v>
+        <v>0.723404255319149</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="G20" t="n">
         <v>0.85</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8159090909090909</v>
+        <v>0.8340909090909091</v>
       </c>
     </row>
     <row r="21">
@@ -1095,19 +1095,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7368421052631577</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8136363636363635</v>
+        <v>0.8636363636363636</v>
       </c>
     </row>
     <row r="22">
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.4933333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4864864864864865</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="G22" t="n">
         <v>0.9</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6227272727272728</v>
+        <v>0.8772727272727272</v>
       </c>
     </row>
     <row r="23">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.7368421052631577</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5</v>
+        <v>0.8136363636363635</v>
       </c>
     </row>
     <row r="24">
@@ -1191,19 +1191,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.4933333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4864864864864865</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="G24" t="n">
         <v>0.9</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6227272727272728</v>
+        <v>0.8772727272727272</v>
       </c>
     </row>
     <row r="25">
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>0.8205128205128205</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5</v>
+        <v>0.8727272727272728</v>
       </c>
     </row>
     <row r="26">
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.7555555555555556</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7545454545454545</v>
+        <v>0.8522727272727272</v>
       </c>
     </row>
     <row r="27">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.8292682926829269</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="G27" t="n">
-        <v>0.55</v>
+        <v>0.85</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7022727272727273</v>
+        <v>0.8886363636363637</v>
       </c>
     </row>
     <row r="28">
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.8260869565217392</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7545454545454545</v>
+        <v>0.9113636363636364</v>
       </c>
     </row>
     <row r="29">
@@ -1351,19 +1351,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.88</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="G29" t="n">
-        <v>0.55</v>
+        <v>0.85</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7022727272727273</v>
+        <v>0.8704545454545455</v>
       </c>
     </row>
     <row r="30">
@@ -1492,6 +1492,1030 @@
       </c>
       <c r="H33" t="n">
         <v>0.9318181818181818</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.845360824742268</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.8367346938775511</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.7789351851851851</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8686868686868686</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.7997685185185186</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8282828282828283</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.803921568627451</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.7418981481481481</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.854368932038835</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.7546296296296295</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.795138888888889</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>svc_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.7361111111111112</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8602150537634408</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.8240740740740742</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>svc_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.7962962962962963</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.744212962962963</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.851063829787234</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.7870370370370371</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.7685185185185186</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.851063829787234</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.845360824742268</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.8367346938775511</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.7789351851851851</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>xgbclassifier_smote_splashing</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.8182870370370371</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>xgbclassifier_splashing</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.8865979381443299</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.8368055555555556</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>catboostclassifier_smote_splashing</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.8865979381443299</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.8368055555555556</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>catboostclassifier_splashing</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.8391203703703703</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.8681818181818182</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.7804878048780488</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.8545454545454545</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.7391304347826088</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.8431818181818183</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8000000000000002</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8260869565217392</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.7307692307692307</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.9113636363636364</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>svc_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.8068181818181818</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.7826086956521738</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.8772727272727272</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>svc_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.7894736842105262</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.8477272727272728</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.8681818181818182</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.9136363636363636</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.8863636363636364</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.8780487804878048</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.9227272727272726</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>xgbclassifier_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.9068181818181819</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>xgbclassifier_net_impact</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.8318181818181818</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>catboostclassifier_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.8780487804878048</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.9227272727272726</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>catboostclassifier_net_impact</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.8780487804878048</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.9227272727272726</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_modelling2.xlsx
+++ b/results/metrics_modelling2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2518,6 +2518,1030 @@
         <v>0.9227272727272726</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.7685185185185186</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.8101851851851851</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.8282828282828283</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.803921568627451</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.7418981481481481</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.8035714285714286</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.7650462962962963</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.8287037037037036</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>svc_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.7465277777777777</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.8182870370370371</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>svc_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.7465277777777777</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.8182870370370371</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.8910891089108911</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.8206018518518519</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.8979591836734694</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.8472222222222222</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.8391203703703703</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>xgbclassifier_smote_splashing</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.8182870370370371</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>xgbclassifier_splashing</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.8182870370370371</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>catboostclassifier_smote_splashing</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.8865979381443299</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.8368055555555556</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>catboostclassifier_splashing</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.8391203703703703</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.8681818181818182</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.8386363636363635</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.7555555555555556</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.8522727272727272</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.8000000000000002</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.8863636363636364</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>svc_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.7222222222222223</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.7977272727272726</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.8863636363636364</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>svc_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.7027027027027027</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.7886363636363636</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.859090909090909</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.8704545454545455</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.7826086956521738</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.8772727272727272</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.8704545454545455</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>xgbclassifier_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.8421052631578948</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.8818181818181818</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>xgbclassifier_net_impact</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.8318181818181818</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>catboostclassifier_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.8780487804878048</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.9227272727272726</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>catboostclassifier_net_impact</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.9466666666666667</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.9318181818181818</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/metrics_modelling2.xlsx
+++ b/results/metrics_modelling2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3542,6 +3542,2054 @@
         <v>0.9318181818181818</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.845360824742268</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.8367346938775511</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.7789351851851851</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.8686868686868686</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.7997685185185186</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.7523148148148149</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.8035714285714286</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.7650462962962963</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.851063829787234</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>svc_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.7361111111111112</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.8723404255319149</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.8913043478260869</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.8344907407407407</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>svc_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.7962962962962963</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.744212962962963</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.8297872340425533</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.8478260869565217</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.7766203703703703</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.7685185185185186</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.795138888888889</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.845360824742268</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.8367346938775511</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.7789351851851851</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>xgbclassifier_smote_splashing</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9052631578947369</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.9148936170212766</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.8738425925925927</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>xgbclassifier_splashing</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.8865979381443299</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.8368055555555556</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>catboostclassifier_smote_splashing</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.8553240740740742</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>catboostclassifier_splashing</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.8391203703703703</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.8681818181818182</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.8386363636363635</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.8613636363636364</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.8727272727272728</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.8863636363636364</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>svc_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.8068181818181818</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.7826086956521738</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.8772727272727272</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>svc_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.7058823529411764</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.7818181818181819</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.8681818181818182</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.9136363636363636</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.8863636363636364</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.9136363636363636</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>xgbclassifier_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.8421052631578948</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.8818181818181818</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>xgbclassifier_net_impact</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.8318181818181818</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>catboostclassifier_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.9045454545454544</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>catboostclassifier_net_impact</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.8780487804878048</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.9227272727272726</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.845360824742268</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.8367346938775511</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.7789351851851851</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.8269230769230769</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.7812500000000001</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.7523148148148149</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.8035714285714286</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.7650462962962963</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.8287037037037036</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>svc_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.7465277777777777</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.8659793814432989</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.8078703703703703</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>svc_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.7465277777777777</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.8979591836734694</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.8472222222222222</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.8910891089108911</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.8206018518518519</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.9072164948453607</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.8979591836734694</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.8657407407407407</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.8391203703703703</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>xgbclassifier_smote_splashing</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.8101851851851851</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>xgbclassifier_splashing</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.8182870370370371</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>catboostclassifier_smote_splashing</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.8979591836734694</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.8472222222222222</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>catboostclassifier_splashing</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.8391203703703703</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.8681818181818182</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.8386363636363635</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.7555555555555556</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.8522727272727272</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.8000000000000002</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.8863636363636364</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>svc_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.7222222222222223</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.7977272727272726</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.8863636363636364</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>svc_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.7368421052631577</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.8136363636363635</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.859090909090909</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.8704545454545455</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.7826086956521738</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.8772727272727272</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.8704545454545455</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>xgbclassifier_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.8421052631578948</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.8818181818181818</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>xgbclassifier_net_impact</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.8318181818181818</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>catboostclassifier_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.9045454545454544</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>catboostclassifier_net_impact</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0.9466666666666667</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.9318181818181818</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/metrics_modelling2.xlsx
+++ b/results/metrics_modelling2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -867,23 +867,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>xgbclassifier_smote_splashing</t>
+          <t>xgbclassifier_ohe_smote_splashing</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8686868686868686</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G14" t="n">
         <v>0.8958333333333334</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7997685185185186</v>
+        <v>0.8368055555555556</v>
       </c>
     </row>
     <row r="15">
@@ -899,7 +899,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xgbclassifier_splashing</t>
+          <t>xgbclassifier_smote_splashing</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -931,23 +931,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>catboostclassifier_smote_splashing</t>
+          <t>xgbclassifier_ohe_splashing</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8865979381443299</v>
+        <v>0.8514851485148515</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.8113207547169812</v>
       </c>
       <c r="G16" t="n">
         <v>0.8958333333333334</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8368055555555556</v>
+        <v>0.7627314814814815</v>
       </c>
     </row>
     <row r="17">
@@ -963,23 +963,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>catboostclassifier_splashing</t>
+          <t>xgbclassifier_splashing</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9</v>
+        <v>0.8686868686868686</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8653846153846154</v>
+        <v>0.8431372549019608</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9375</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8391203703703703</v>
+        <v>0.7997685185185186</v>
       </c>
     </row>
     <row r="18">
@@ -990,28 +990,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>logisticregression_smote_net_impact_onehot</t>
+          <t>catboostclassifier_ohe_smote_splashing</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.8533333333333334</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8681818181818182</v>
+        <v>0.8368055555555556</v>
       </c>
     </row>
     <row r="19">
@@ -1022,28 +1022,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>logisticregression_net_impact_onehot</t>
+          <t>catboostclassifier_smote_splashing</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.88</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7804878048780488</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8545454545454545</v>
+        <v>0.8368055555555556</v>
       </c>
     </row>
     <row r="20">
@@ -1054,28 +1054,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>logisticregression_smote_net_impact_ordenc</t>
+          <t>catboostclassifier_ohe_splashing</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.84</v>
       </c>
       <c r="E20" t="n">
-        <v>0.723404255319149</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.86</v>
       </c>
       <c r="G20" t="n">
-        <v>0.85</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8340909090909091</v>
+        <v>0.8182870370370371</v>
       </c>
     </row>
     <row r="21">
@@ -1086,28 +1086,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>logisticregression_net_impact_ordenc</t>
+          <t>catboostclassifier_splashing</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.9</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8</v>
+        <v>0.9375</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.8391203703703703</v>
       </c>
     </row>
     <row r="22">
@@ -1123,23 +1123,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>svc_smote_net_impact_onehot</t>
+          <t>logisticregression_smote_net_impact_onehot</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7826086956521738</v>
+        <v>0.7659574468085106</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G22" t="n">
         <v>0.9</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8772727272727272</v>
+        <v>0.8681818181818182</v>
       </c>
     </row>
     <row r="23">
@@ -1155,23 +1155,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>svc_net_impact_onehot</t>
+          <t>logisticregression_net_impact_onehot</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.88</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7368421052631577</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8136363636363635</v>
+        <v>0.8545454545454545</v>
       </c>
     </row>
     <row r="24">
@@ -1187,23 +1187,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>svc_smote_net_impact_ordenc</t>
+          <t>logisticregression_smote_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7826086956521738</v>
+        <v>0.723404255319149</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8772727272727272</v>
+        <v>0.8340909090909091</v>
       </c>
     </row>
     <row r="25">
@@ -1219,23 +1219,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>svc_net_impact_ordenc</t>
+          <t>logisticregression_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8</v>
       </c>
       <c r="G25" t="n">
         <v>0.8</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8727272727272728</v>
+        <v>0.8636363636363636</v>
       </c>
     </row>
     <row r="26">
@@ -1251,23 +1251,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_net_impact_onehot</t>
+          <t>svc_smote_net_impact_onehot</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7555555555555556</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="F26" t="n">
-        <v>0.68</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="G26" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8522727272727272</v>
+        <v>0.8772727272727272</v>
       </c>
     </row>
     <row r="27">
@@ -1283,23 +1283,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_net_impact_onehot</t>
+          <t>svc_net_impact_onehot</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8292682926829269</v>
+        <v>0.7368421052631577</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G27" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8886363636363637</v>
+        <v>0.8136363636363635</v>
       </c>
     </row>
     <row r="28">
@@ -1315,23 +1315,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
+          <t>svc_smote_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8260869565217392</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="G28" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9113636363636364</v>
+        <v>0.8772727272727272</v>
       </c>
     </row>
     <row r="29">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_net_impact_ordenc</t>
+          <t>svc_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.88</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7906976744186046</v>
+        <v>0.8205128205128205</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="G29" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8704545454545455</v>
+        <v>0.8727272727272728</v>
       </c>
     </row>
     <row r="30">
@@ -1379,23 +1379,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>xgbclassifier_smote_net_impact</t>
+          <t>kneighborsclassifier_smote_net_impact_onehot</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8717948717948718</v>
+        <v>0.7555555555555556</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.68</v>
       </c>
       <c r="G30" t="n">
         <v>0.85</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9068181818181819</v>
+        <v>0.8522727272727272</v>
       </c>
     </row>
     <row r="31">
@@ -1411,23 +1411,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>xgbclassifier_net_impact</t>
+          <t>kneighborsclassifier_net_impact_onehot</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.8292682926829269</v>
       </c>
       <c r="F31" t="n">
-        <v>0.875</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8318181818181818</v>
+        <v>0.8886363636363637</v>
       </c>
     </row>
     <row r="32">
@@ -1443,23 +1443,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>catboostclassifier_smote_net_impact</t>
+          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8780487804878048</v>
+        <v>0.8260869565217392</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9227272727272726</v>
+        <v>0.9113636363636364</v>
       </c>
     </row>
     <row r="33">
@@ -1475,285 +1475,285 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>catboostclassifier_net_impact</t>
+          <t>kneighborsclassifier_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.88</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9318181818181818</v>
+        <v>0.8704545454545455</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_full</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>logisticregression_smote_splashing_onehot</t>
+          <t>xgbclassifier_ohe_smote_net_impact</t>
         </is>
       </c>
       <c r="D34" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8421052631578948</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="G34" t="n">
         <v>0.8</v>
       </c>
-      <c r="E34" t="n">
-        <v>0.845360824742268</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.8367346938775511</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.8541666666666666</v>
-      </c>
       <c r="H34" t="n">
-        <v>0.7789351851851851</v>
+        <v>0.8818181818181818</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_full</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>logisticregression_splashing_onehot</t>
+          <t>xgbclassifier_smote_net_impact</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8686868686868686</v>
+        <v>0.8717948717948718</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.85</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7997685185185186</v>
+        <v>0.9068181818181819</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_full</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>logisticregression_smote_splashing_ordenc</t>
+          <t>xgbclassifier_ohe_net_impact</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8282828282828283</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="F36" t="n">
-        <v>0.803921568627451</v>
+        <v>0.875</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.7</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7418981481481481</v>
+        <v>0.8318181818181818</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_full</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>logisticregression_splashing_ordenc</t>
+          <t>xgbclassifier_net_impact</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.8</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E37" t="n">
-        <v>0.854368932038835</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8</v>
+        <v>0.875</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.7</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7546296296296295</v>
+        <v>0.8318181818181818</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_full</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>svc_smote_splashing_onehot</t>
+          <t>catboostclassifier_ohe_smote_net_impact</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.8</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8780487804878048</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8125</v>
+        <v>0.9</v>
       </c>
       <c r="H38" t="n">
-        <v>0.795138888888889</v>
+        <v>0.9227272727272726</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_full</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>svc_splashing_onehot</t>
+          <t>catboostclassifier_smote_net_impact</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8780487804878048</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7361111111111112</v>
+        <v>0.9227272727272726</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_full</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>svc_smote_splashing_ordenc</t>
+          <t>catboostclassifier_ohe_net_impact</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8602150537634408</v>
+        <v>0.9</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8240740740740742</v>
+        <v>0.9318181818181818</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_full</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>svc_splashing_ordenc</t>
+          <t>catboostclassifier_net_impact</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.9</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7962962962962963</v>
+        <v>0.9</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="H41" t="n">
-        <v>0.744212962962963</v>
+        <v>0.9318181818181818</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1763,29 +1763,29 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_splashing_onehot</t>
+          <t>logisticregression_smote_splashing_onehot</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.8</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F42" t="n">
-        <v>0.851063829787234</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G42" t="n">
         <v>0.8333333333333334</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7870370370370371</v>
+        <v>0.7685185185185186</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1795,29 +1795,29 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_splashing_onehot</t>
+          <t>logisticregression_splashing_onehot</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.84</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8799999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7685185185185186</v>
+        <v>0.8101851851851851</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1827,29 +1827,29 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_splashing_ordenc</t>
+          <t>logisticregression_smote_splashing_ordenc</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="E44" t="n">
-        <v>0.851063829787234</v>
+        <v>0.8282828282828283</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.803921568627451</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7418981481481481</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1859,29 +1859,29 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_splashing_ordenc</t>
+          <t>logisticregression_splashing_ordenc</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.8</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="E45" t="n">
-        <v>0.845360824742268</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.9375</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7789351851851851</v>
+        <v>0.7650462962962963</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1891,29 +1891,29 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>xgbclassifier_smote_splashing</t>
+          <t>svc_smote_splashing_onehot</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.84</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E46" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="F46" t="n">
-        <v>0.86</v>
+        <v>0.8627450980392157</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8182870370370371</v>
+        <v>0.8287037037037036</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1923,29 +1923,29 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>xgbclassifier_splashing</t>
+          <t>svc_splashing_onehot</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8865979381443299</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9375</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8368055555555556</v>
+        <v>0.7465277777777777</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1955,29 +1955,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>catboostclassifier_smote_splashing</t>
+          <t>svc_smote_splashing_ordenc</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.84</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8865979381443299</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.86</v>
       </c>
       <c r="G48" t="n">
         <v>0.8958333333333334</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8368055555555556</v>
+        <v>0.8182870370370371</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1987,413 +1987,413 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>catboostclassifier_splashing</t>
+          <t>svc_splashing_ordenc</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8653846153846154</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="G49" t="n">
         <v>0.9375</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8391203703703703</v>
+        <v>0.7465277777777777</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>logisticregression_smote_net_impact_onehot</t>
+          <t>kneighborsclassifier_smote_splashing_onehot</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.84</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.86</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8681818181818182</v>
+        <v>0.8182870370370371</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>logisticregression_net_impact_onehot</t>
+          <t>kneighborsclassifier_splashing_onehot</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.88</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E51" t="n">
-        <v>0.7804878048780488</v>
+        <v>0.8910891089108911</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8</v>
+        <v>0.9375</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8545454545454545</v>
+        <v>0.8206018518518519</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>logisticregression_smote_net_impact_ordenc</t>
+          <t>kneighborsclassifier_smote_splashing_ordenc</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.84</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7391304347826088</v>
+        <v>0.8979591836734694</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.88</v>
       </c>
       <c r="G52" t="n">
-        <v>0.85</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8431818181818183</v>
+        <v>0.8472222222222222</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>logisticregression_net_impact_ordenc</t>
+          <t>kneighborsclassifier_splashing_ordenc</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.9</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8</v>
+        <v>0.9375</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.8391203703703703</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>svc_smote_net_impact_onehot</t>
+          <t>xgbclassifier_ohe_smote_splashing</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.84</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8260869565217392</v>
+        <v>0.8799999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="G54" t="n">
-        <v>0.95</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9113636363636364</v>
+        <v>0.8101851851851851</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>svc_net_impact_onehot</t>
+          <t>xgbclassifier_smote_splashing</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.86</v>
       </c>
       <c r="G55" t="n">
-        <v>0.65</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8068181818181818</v>
+        <v>0.8182870370370371</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>svc_smote_net_impact_ordenc</t>
+          <t>xgbclassifier_ohe_splashing</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.84</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7826086956521738</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="F56" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.86</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8772727272727272</v>
+        <v>0.8182870370370371</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>svc_net_impact_ordenc</t>
+          <t>xgbclassifier_splashing</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.84</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7894736842105262</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.86</v>
       </c>
       <c r="G57" t="n">
-        <v>0.75</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8477272727272728</v>
+        <v>0.8182870370370371</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_net_impact_onehot</t>
+          <t>catboostclassifier_ohe_smote_splashing</t>
         </is>
       </c>
       <c r="D58" t="n">
         <v>0.8533333333333334</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8681818181818182</v>
+        <v>0.8368055555555556</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_net_impact_onehot</t>
+          <t>catboostclassifier_smote_splashing</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.92</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E59" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H59" t="n">
-        <v>0.9136363636363636</v>
+        <v>0.8368055555555556</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
+          <t>catboostclassifier_ohe_splashing</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.88</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E60" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="F60" t="n">
-        <v>0.72</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.8368055555555556</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_net_impact_ordenc</t>
+          <t>catboostclassifier_splashing</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8780487804878048</v>
+        <v>0.9</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9</v>
+        <v>0.9375</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9227272727272726</v>
+        <v>0.8391203703703703</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2403,29 +2403,29 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>xgbclassifier_smote_net_impact</t>
+          <t>logisticregression_smote_net_impact_onehot</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E62" t="n">
-        <v>0.8717948717948718</v>
+        <v>0.7659574468085106</v>
       </c>
       <c r="F62" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G62" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H62" t="n">
-        <v>0.9068181818181819</v>
+        <v>0.8681818181818182</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2435,29 +2435,29 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>xgbclassifier_net_impact</t>
+          <t>logisticregression_net_impact_onehot</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.88</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="F63" t="n">
-        <v>0.875</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="G63" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8318181818181818</v>
+        <v>0.8386363636363635</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2467,29 +2467,29 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>catboostclassifier_smote_net_impact</t>
+          <t>logisticregression_smote_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E64" t="n">
-        <v>0.8780487804878048</v>
+        <v>0.7555555555555556</v>
       </c>
       <c r="F64" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.68</v>
       </c>
       <c r="G64" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H64" t="n">
-        <v>0.9227272727272726</v>
+        <v>0.8522727272727272</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2499,23 +2499,23 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>catboostclassifier_net_impact</t>
+          <t>logisticregression_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E65" t="n">
-        <v>0.8780487804878048</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H65" t="n">
-        <v>0.9227272727272726</v>
+        <v>0.8636363636363636</v>
       </c>
     </row>
     <row r="66">
@@ -2526,28 +2526,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>logisticregression_smote_splashing_onehot</t>
+          <t>svc_smote_net_impact_onehot</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.88</v>
       </c>
       <c r="E66" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.72</v>
       </c>
       <c r="G66" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="H66" t="n">
-        <v>0.7685185185185186</v>
+        <v>0.8863636363636364</v>
       </c>
     </row>
     <row r="67">
@@ -2558,28 +2558,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>logisticregression_splashing_onehot</t>
+          <t>svc_net_impact_onehot</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.84</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E67" t="n">
-        <v>0.8799999999999999</v>
+        <v>0.7222222222222223</v>
       </c>
       <c r="F67" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8125</v>
       </c>
       <c r="G67" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.65</v>
       </c>
       <c r="H67" t="n">
-        <v>0.8101851851851851</v>
+        <v>0.7977272727272726</v>
       </c>
     </row>
     <row r="68">
@@ -2590,28 +2590,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>logisticregression_smote_splashing_ordenc</t>
+          <t>svc_smote_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.88</v>
       </c>
       <c r="E68" t="n">
-        <v>0.8282828282828283</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="F68" t="n">
-        <v>0.803921568627451</v>
+        <v>0.72</v>
       </c>
       <c r="G68" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.9</v>
       </c>
       <c r="H68" t="n">
-        <v>0.7418981481481481</v>
+        <v>0.8863636363636364</v>
       </c>
     </row>
     <row r="69">
@@ -2622,28 +2622,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>logisticregression_splashing_ordenc</t>
+          <t>svc_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8653846153846154</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9375</v>
+        <v>0.65</v>
       </c>
       <c r="H69" t="n">
-        <v>0.7650462962962963</v>
+        <v>0.7886363636363636</v>
       </c>
     </row>
     <row r="70">
@@ -2654,28 +2654,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>svc_smote_splashing_onehot</t>
+          <t>kneighborsclassifier_smote_net_impact_onehot</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.84</v>
       </c>
       <c r="E70" t="n">
-        <v>0.888888888888889</v>
+        <v>0.75</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8627450980392157</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="G70" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8287037037037036</v>
+        <v>0.859090909090909</v>
       </c>
     </row>
     <row r="71">
@@ -2686,28 +2686,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>svc_splashing_onehot</t>
+          <t>kneighborsclassifier_net_impact_onehot</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="E71" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="G71" t="n">
-        <v>0.9375</v>
+        <v>0.85</v>
       </c>
       <c r="H71" t="n">
-        <v>0.7465277777777777</v>
+        <v>0.8704545454545455</v>
       </c>
     </row>
     <row r="72">
@@ -2718,28 +2718,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>svc_smote_splashing_ordenc</t>
+          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.84</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E72" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="F72" t="n">
-        <v>0.86</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="G72" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8182870370370371</v>
+        <v>0.8772727272727272</v>
       </c>
     </row>
     <row r="73">
@@ -2750,28 +2750,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>svc_splashing_ordenc</t>
+          <t>kneighborsclassifier_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="E73" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9375</v>
+        <v>0.85</v>
       </c>
       <c r="H73" t="n">
-        <v>0.7465277777777777</v>
+        <v>0.8704545454545455</v>
       </c>
     </row>
     <row r="74">
@@ -2782,28 +2782,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_splashing_onehot</t>
+          <t>xgbclassifier_ohe_smote_net_impact</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="E74" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.8421052631578948</v>
       </c>
       <c r="F74" t="n">
-        <v>0.86</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G74" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8182870370370371</v>
+        <v>0.8818181818181818</v>
       </c>
     </row>
     <row r="75">
@@ -2814,28 +2814,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_splashing_onehot</t>
+          <t>xgbclassifier_smote_net_impact</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.92</v>
       </c>
       <c r="E75" t="n">
-        <v>0.8910891089108911</v>
+        <v>0.8421052631578948</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8490566037735849</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9375</v>
+        <v>0.8</v>
       </c>
       <c r="H75" t="n">
-        <v>0.8206018518518519</v>
+        <v>0.8818181818181818</v>
       </c>
     </row>
     <row r="76">
@@ -2846,28 +2846,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_splashing_ordenc</t>
+          <t>xgbclassifier_ohe_net_impact</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E76" t="n">
-        <v>0.8979591836734694</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="F76" t="n">
-        <v>0.88</v>
+        <v>0.875</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.7</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8472222222222222</v>
+        <v>0.8318181818181818</v>
       </c>
     </row>
     <row r="77">
@@ -2878,28 +2878,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_splashing_ordenc</t>
+          <t>xgbclassifier_net_impact</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8653846153846154</v>
+        <v>0.875</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9375</v>
+        <v>0.7</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8391203703703703</v>
+        <v>0.8318181818181818</v>
       </c>
     </row>
     <row r="78">
@@ -2910,28 +2910,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>xgbclassifier_smote_splashing</t>
+          <t>catboostclassifier_ohe_smote_net_impact</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.84</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="E78" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="F78" t="n">
-        <v>0.86</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8182870370370371</v>
+        <v>0.9045454545454544</v>
       </c>
     </row>
     <row r="79">
@@ -2942,28 +2942,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>xgbclassifier_splashing</t>
+          <t>catboostclassifier_smote_net_impact</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.84</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.8780487804878048</v>
       </c>
       <c r="F79" t="n">
-        <v>0.86</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G79" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8182870370370371</v>
+        <v>0.9227272727272726</v>
       </c>
     </row>
     <row r="80">
@@ -2974,28 +2974,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>catboostclassifier_smote_splashing</t>
+          <t>catboostclassifier_ohe_net_impact</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="E80" t="n">
-        <v>0.8865979381443299</v>
+        <v>0.8717948717948718</v>
       </c>
       <c r="F80" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.85</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8368055555555556</v>
+        <v>0.9068181818181819</v>
       </c>
     </row>
     <row r="81">
@@ -3006,546 +3006,546 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>catboostclassifier_splashing</t>
+          <t>catboostclassifier_net_impact</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="E81" t="n">
         <v>0.9</v>
       </c>
       <c r="F81" t="n">
-        <v>0.8653846153846154</v>
+        <v>0.9</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9375</v>
+        <v>0.9</v>
       </c>
       <c r="H81" t="n">
-        <v>0.8391203703703703</v>
+        <v>0.9318181818181818</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>logisticregression_smote_net_impact_onehot</t>
+          <t>logisticregression_smote_splashing_onehot</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="E82" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.845360824742268</v>
       </c>
       <c r="F82" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8681818181818182</v>
+        <v>0.7789351851851851</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>logisticregression_net_impact_onehot</t>
+          <t>logisticregression_splashing_onehot</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.88</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="E83" t="n">
-        <v>0.7692307692307692</v>
+        <v>0.86</v>
       </c>
       <c r="F83" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8269230769230769</v>
       </c>
       <c r="G83" t="n">
-        <v>0.75</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H83" t="n">
-        <v>0.8386363636363635</v>
+        <v>0.7812500000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>logisticregression_smote_net_impact_ordenc</t>
+          <t>logisticregression_smote_splashing_ordenc</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7555555555555556</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="F84" t="n">
-        <v>0.68</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="G84" t="n">
-        <v>0.85</v>
+        <v>0.875</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8522727272727272</v>
+        <v>0.7523148148148149</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>logisticregression_net_impact_ordenc</t>
+          <t>logisticregression_splashing_ordenc</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="G85" t="n">
-        <v>0.8</v>
+        <v>0.9375</v>
       </c>
       <c r="H85" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.7650462962962963</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>svc_smote_net_impact_onehot</t>
+          <t>svc_smote_splashing_onehot</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.88</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="F86" t="n">
-        <v>0.72</v>
+        <v>0.8627450980392157</v>
       </c>
       <c r="G86" t="n">
-        <v>0.9</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H86" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.8287037037037036</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>svc_net_impact_onehot</t>
+          <t>svc_splashing_onehot</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="E87" t="n">
-        <v>0.7222222222222223</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="F87" t="n">
-        <v>0.8125</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="G87" t="n">
-        <v>0.65</v>
+        <v>0.9375</v>
       </c>
       <c r="H87" t="n">
-        <v>0.7977272727272726</v>
+        <v>0.7465277777777777</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>svc_smote_net_impact_ordenc</t>
+          <t>svc_smote_splashing_ordenc</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.88</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8659793814432989</v>
       </c>
       <c r="F88" t="n">
-        <v>0.72</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G88" t="n">
-        <v>0.9</v>
+        <v>0.875</v>
       </c>
       <c r="H88" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.8078703703703703</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>svc_net_impact_ordenc</t>
+          <t>svc_splashing_ordenc</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="E89" t="n">
-        <v>0.7027027027027027</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="G89" t="n">
-        <v>0.65</v>
+        <v>0.9375</v>
       </c>
       <c r="H89" t="n">
-        <v>0.7886363636363636</v>
+        <v>0.7465277777777777</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_net_impact_onehot</t>
+          <t>kneighborsclassifier_smote_splashing_onehot</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.84</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E90" t="n">
-        <v>0.75</v>
+        <v>0.8979591836734694</v>
       </c>
       <c r="F90" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.88</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H90" t="n">
-        <v>0.859090909090909</v>
+        <v>0.8472222222222222</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_net_impact_onehot</t>
+          <t>kneighborsclassifier_splashing_onehot</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.88</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E91" t="n">
-        <v>0.7906976744186046</v>
+        <v>0.8910891089108911</v>
       </c>
       <c r="F91" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="G91" t="n">
-        <v>0.85</v>
+        <v>0.9375</v>
       </c>
       <c r="H91" t="n">
-        <v>0.8704545454545455</v>
+        <v>0.8206018518518519</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
+          <t>kneighborsclassifier_smote_splashing_ordenc</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.88</v>
       </c>
       <c r="E92" t="n">
-        <v>0.7826086956521738</v>
+        <v>0.9072164948453607</v>
       </c>
       <c r="F92" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.8979591836734694</v>
       </c>
       <c r="G92" t="n">
-        <v>0.9</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H92" t="n">
-        <v>0.8772727272727272</v>
+        <v>0.8657407407407407</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_net_impact_ordenc</t>
+          <t>kneighborsclassifier_splashing_ordenc</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.88</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E93" t="n">
-        <v>0.7906976744186046</v>
+        <v>0.9</v>
       </c>
       <c r="F93" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="G93" t="n">
-        <v>0.85</v>
+        <v>0.9375</v>
       </c>
       <c r="H93" t="n">
-        <v>0.8704545454545455</v>
+        <v>0.8391203703703703</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>xgbclassifier_smote_net_impact</t>
+          <t>xgbclassifier_ohe_smote_splashing</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="E94" t="n">
-        <v>0.8421052631578948</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="F94" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.86</v>
       </c>
       <c r="G94" t="n">
-        <v>0.8</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H94" t="n">
-        <v>0.8818181818181818</v>
+        <v>0.8182870370370371</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>xgbclassifier_net_impact</t>
+          <t>xgbclassifier_smote_splashing</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.84</v>
       </c>
       <c r="E95" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.8799999999999999</v>
       </c>
       <c r="F95" t="n">
-        <v>0.875</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="G95" t="n">
-        <v>0.7</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H95" t="n">
-        <v>0.8318181818181818</v>
+        <v>0.8101851851851851</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>catboostclassifier_smote_net_impact</t>
+          <t>xgbclassifier_ohe_splashing</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.84</v>
       </c>
       <c r="E96" t="n">
-        <v>0.8780487804878048</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="F96" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.86</v>
       </c>
       <c r="G96" t="n">
-        <v>0.9</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H96" t="n">
-        <v>0.9227272727272726</v>
+        <v>0.8182870370370371</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>catboostclassifier_net_impact</t>
+          <t>xgbclassifier_splashing</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.84</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="F97" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="G97" t="n">
-        <v>0.9</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H97" t="n">
-        <v>0.9318181818181818</v>
+        <v>0.8182870370370371</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3555,29 +3555,29 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>logisticregression_smote_splashing_onehot</t>
+          <t>catboostclassifier_ohe_smote_splashing</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.8</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E98" t="n">
-        <v>0.845360824742268</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="F98" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G98" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H98" t="n">
-        <v>0.7789351851851851</v>
+        <v>0.8368055555555556</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3587,29 +3587,29 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>logisticregression_splashing_onehot</t>
+          <t>catboostclassifier_smote_splashing</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8686868686868686</v>
+        <v>0.8979591836734694</v>
       </c>
       <c r="F99" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.88</v>
       </c>
       <c r="G99" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H99" t="n">
-        <v>0.7997685185185186</v>
+        <v>0.8472222222222222</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3619,29 +3619,29 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>logisticregression_smote_splashing_ordenc</t>
+          <t>catboostclassifier_ohe_splashing</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E100" t="n">
-        <v>0.8400000000000001</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="F100" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G100" t="n">
-        <v>0.875</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H100" t="n">
-        <v>0.7523148148148149</v>
+        <v>0.8368055555555556</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3651,413 +3651,413 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>logisticregression_splashing_ordenc</t>
+          <t>catboostclassifier_splashing</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E101" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F101" t="n">
         <v>0.8653846153846154</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0.8035714285714286</v>
       </c>
       <c r="G101" t="n">
         <v>0.9375</v>
       </c>
       <c r="H101" t="n">
-        <v>0.7650462962962963</v>
+        <v>0.8391203703703703</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>svc_smote_splashing_onehot</t>
+          <t>logisticregression_smote_net_impact_onehot</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E102" t="n">
-        <v>0.851063829787234</v>
+        <v>0.7659574468085106</v>
       </c>
       <c r="F102" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G102" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="H102" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.8681818181818182</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>svc_splashing_onehot</t>
+          <t>logisticregression_net_impact_onehot</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.88</v>
       </c>
       <c r="E103" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="F103" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="G103" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="H103" t="n">
-        <v>0.7361111111111112</v>
+        <v>0.8386363636363635</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>svc_smote_splashing_ordenc</t>
+          <t>logisticregression_smote_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.84</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E104" t="n">
-        <v>0.8723404255319149</v>
+        <v>0.7555555555555556</v>
       </c>
       <c r="F104" t="n">
-        <v>0.8913043478260869</v>
+        <v>0.68</v>
       </c>
       <c r="G104" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.85</v>
       </c>
       <c r="H104" t="n">
-        <v>0.8344907407407407</v>
+        <v>0.8522727272727272</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>svc_splashing_ordenc</t>
+          <t>logisticregression_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E105" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="F105" t="n">
-        <v>0.7962962962962963</v>
+        <v>0.8</v>
       </c>
       <c r="G105" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="H105" t="n">
-        <v>0.744212962962963</v>
+        <v>0.8636363636363636</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_splashing_onehot</t>
+          <t>svc_smote_net_impact_onehot</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.88</v>
       </c>
       <c r="E106" t="n">
-        <v>0.8297872340425533</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>0.8478260869565217</v>
+        <v>0.72</v>
       </c>
       <c r="G106" t="n">
-        <v>0.8125</v>
+        <v>0.9</v>
       </c>
       <c r="H106" t="n">
-        <v>0.7766203703703703</v>
+        <v>0.8863636363636364</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_splashing_onehot</t>
+          <t>svc_net_impact_onehot</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E107" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7222222222222223</v>
       </c>
       <c r="F107" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8125</v>
       </c>
       <c r="G107" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.65</v>
       </c>
       <c r="H107" t="n">
-        <v>0.7685185185185186</v>
+        <v>0.7977272727272726</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_splashing_ordenc</t>
+          <t>svc_smote_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="E108" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="F108" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.72</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8125</v>
+        <v>0.9</v>
       </c>
       <c r="H108" t="n">
-        <v>0.795138888888889</v>
+        <v>0.8863636363636364</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_splashing_ordenc</t>
+          <t>svc_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.8</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E109" t="n">
-        <v>0.845360824742268</v>
+        <v>0.7368421052631577</v>
       </c>
       <c r="F109" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G109" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.7</v>
       </c>
       <c r="H109" t="n">
-        <v>0.7789351851851851</v>
+        <v>0.8136363636363635</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>xgbclassifier_smote_splashing</t>
+          <t>kneighborsclassifier_smote_net_impact_onehot</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="E110" t="n">
-        <v>0.9052631578947369</v>
+        <v>0.75</v>
       </c>
       <c r="F110" t="n">
-        <v>0.9148936170212766</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="G110" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="H110" t="n">
-        <v>0.8738425925925927</v>
+        <v>0.859090909090909</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>xgbclassifier_splashing</t>
+          <t>kneighborsclassifier_net_impact_onehot</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.88</v>
       </c>
       <c r="E111" t="n">
-        <v>0.8865979381443299</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="F111" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="G111" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.85</v>
       </c>
       <c r="H111" t="n">
-        <v>0.8368055555555556</v>
+        <v>0.8704545454545455</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>catboostclassifier_smote_splashing</t>
+          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D112" t="n">
         <v>0.8666666666666667</v>
       </c>
       <c r="E112" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="F112" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="H112" t="n">
-        <v>0.8553240740740742</v>
+        <v>0.8772727272727272</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>catboostclassifier_splashing</t>
+          <t>kneighborsclassifier_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.88</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="F113" t="n">
-        <v>0.8653846153846154</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="G113" t="n">
-        <v>0.9375</v>
+        <v>0.85</v>
       </c>
       <c r="H113" t="n">
-        <v>0.8391203703703703</v>
+        <v>0.8704545454545455</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4067,29 +4067,29 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>logisticregression_smote_net_impact_onehot</t>
+          <t>xgbclassifier_ohe_smote_net_impact</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.92</v>
       </c>
       <c r="E114" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.8421052631578948</v>
       </c>
       <c r="F114" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G114" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H114" t="n">
-        <v>0.8681818181818182</v>
+        <v>0.8818181818181818</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4099,29 +4099,29 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>logisticregression_net_impact_onehot</t>
+          <t>xgbclassifier_smote_net_impact</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="E115" t="n">
-        <v>0.7692307692307692</v>
+        <v>0.8421052631578948</v>
       </c>
       <c r="F115" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G115" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H115" t="n">
-        <v>0.8386363636363635</v>
+        <v>0.8818181818181818</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4131,29 +4131,29 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>logisticregression_smote_net_impact_ordenc</t>
+          <t>xgbclassifier_ohe_net_impact</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E116" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="F116" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="G116" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="H116" t="n">
-        <v>0.8613636363636364</v>
+        <v>0.8318181818181818</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4163,29 +4163,29 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>logisticregression_net_impact_ordenc</t>
+          <t>xgbclassifier_net_impact</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E117" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="F117" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.875</v>
       </c>
       <c r="G117" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H117" t="n">
-        <v>0.8727272727272728</v>
+        <v>0.8318181818181818</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4195,29 +4195,29 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>svc_smote_net_impact_onehot</t>
+          <t>catboostclassifier_ohe_smote_net_impact</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.88</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="E118" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="F118" t="n">
-        <v>0.72</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="G118" t="n">
         <v>0.9</v>
       </c>
       <c r="H118" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.9045454545454544</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4227,29 +4227,29 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>svc_net_impact_onehot</t>
+          <t>catboostclassifier_smote_net_impact</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.88</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="E119" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="F119" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="G119" t="n">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="H119" t="n">
-        <v>0.8068181818181818</v>
+        <v>0.9045454545454544</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4259,29 +4259,29 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>svc_smote_net_impact_ordenc</t>
+          <t>catboostclassifier_ohe_net_impact</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="E120" t="n">
-        <v>0.7826086956521738</v>
+        <v>0.8717948717948718</v>
       </c>
       <c r="F120" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="G120" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H120" t="n">
-        <v>0.8772727272727272</v>
+        <v>0.9068181818181819</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4291,285 +4291,285 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>svc_net_impact_ordenc</t>
+          <t>catboostclassifier_net_impact</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="E121" t="n">
-        <v>0.7058823529411764</v>
+        <v>0.9</v>
       </c>
       <c r="F121" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9</v>
       </c>
       <c r="G121" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="H121" t="n">
-        <v>0.7818181818181819</v>
+        <v>0.9318181818181818</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_net_impact_onehot</t>
+          <t>logisticregression_smote_splashing_onehot</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="E122" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.845360824742268</v>
       </c>
       <c r="F122" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="G122" t="n">
-        <v>0.9</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="H122" t="n">
-        <v>0.8681818181818182</v>
+        <v>0.7789351851851851</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_net_impact_onehot</t>
+          <t>logisticregression_splashing_onehot</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.92</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="E123" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8686868686868686</v>
       </c>
       <c r="F123" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8431372549019608</v>
       </c>
       <c r="G123" t="n">
-        <v>0.9</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H123" t="n">
-        <v>0.9136363636363636</v>
+        <v>0.7997685185185186</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
+          <t>logisticregression_smote_splashing_ordenc</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.88</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="E124" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8282828282828283</v>
       </c>
       <c r="F124" t="n">
-        <v>0.72</v>
+        <v>0.803921568627451</v>
       </c>
       <c r="G124" t="n">
-        <v>0.9</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="H124" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.7418981481481481</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_net_impact_ordenc</t>
+          <t>logisticregression_splashing_ordenc</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="E125" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.854368932038835</v>
       </c>
       <c r="F125" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8</v>
       </c>
       <c r="G125" t="n">
-        <v>0.9</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H125" t="n">
-        <v>0.9136363636363636</v>
+        <v>0.7546296296296295</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>xgbclassifier_smote_net_impact</t>
+          <t>svc_smote_splashing_onehot</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="E126" t="n">
-        <v>0.8421052631578948</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="F126" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="G126" t="n">
-        <v>0.8</v>
+        <v>0.8125</v>
       </c>
       <c r="H126" t="n">
-        <v>0.8818181818181818</v>
+        <v>0.795138888888889</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>xgbclassifier_net_impact</t>
+          <t>svc_splashing_onehot</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="E127" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="F127" t="n">
-        <v>0.875</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="G127" t="n">
-        <v>0.7</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="H127" t="n">
-        <v>0.8318181818181818</v>
+        <v>0.7361111111111112</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>catboostclassifier_smote_net_impact</t>
+          <t>svc_smote_splashing_ordenc</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="E128" t="n">
-        <v>0.8372093023255814</v>
+        <v>0.8602150537634408</v>
       </c>
       <c r="F128" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G128" t="n">
-        <v>0.9</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H128" t="n">
-        <v>0.9045454545454544</v>
+        <v>0.8240740740740742</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>catboostclassifier_net_impact</t>
+          <t>svc_splashing_ordenc</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="E129" t="n">
-        <v>0.8780487804878048</v>
+        <v>0.8431372549019608</v>
       </c>
       <c r="F129" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7962962962962963</v>
       </c>
       <c r="G129" t="n">
-        <v>0.9</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9227272727272726</v>
+        <v>0.744212962962963</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4579,29 +4579,29 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>logisticregression_smote_splashing_onehot</t>
+          <t>kneighborsclassifier_smote_splashing_onehot</t>
         </is>
       </c>
       <c r="D130" t="n">
         <v>0.8</v>
       </c>
       <c r="E130" t="n">
-        <v>0.845360824742268</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="F130" t="n">
-        <v>0.8367346938775511</v>
+        <v>0.851063829787234</v>
       </c>
       <c r="G130" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H130" t="n">
-        <v>0.7789351851851851</v>
+        <v>0.7870370370370371</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4611,29 +4611,29 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>logisticregression_splashing_onehot</t>
+          <t>kneighborsclassifier_splashing_onehot</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="E131" t="n">
-        <v>0.86</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F131" t="n">
-        <v>0.8269230769230769</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G131" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H131" t="n">
-        <v>0.7812500000000001</v>
+        <v>0.7685185185185186</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4643,29 +4643,29 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>logisticregression_smote_splashing_ordenc</t>
+          <t>kneighborsclassifier_smote_splashing_ordenc</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="E132" t="n">
-        <v>0.8400000000000001</v>
+        <v>0.851063829787234</v>
       </c>
       <c r="F132" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="G132" t="n">
-        <v>0.875</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H132" t="n">
-        <v>0.7523148148148149</v>
+        <v>0.8055555555555556</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4675,29 +4675,29 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>logisticregression_splashing_ordenc</t>
+          <t>kneighborsclassifier_splashing_ordenc</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="E133" t="n">
-        <v>0.8653846153846154</v>
+        <v>0.845360824742268</v>
       </c>
       <c r="F133" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="G133" t="n">
-        <v>0.9375</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="H133" t="n">
-        <v>0.7650462962962963</v>
+        <v>0.7789351851851851</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4707,29 +4707,29 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>svc_smote_splashing_onehot</t>
+          <t>xgbclassifier_ohe_smote_splashing</t>
         </is>
       </c>
       <c r="D134" t="n">
         <v>0.8533333333333334</v>
       </c>
       <c r="E134" t="n">
-        <v>0.888888888888889</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="F134" t="n">
-        <v>0.8627450980392157</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G134" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H134" t="n">
-        <v>0.8287037037037036</v>
+        <v>0.8368055555555556</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4739,29 +4739,29 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>svc_splashing_onehot</t>
+          <t>xgbclassifier_smote_splashing</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="E135" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="F135" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.86</v>
       </c>
       <c r="G135" t="n">
-        <v>0.9375</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H135" t="n">
-        <v>0.7465277777777777</v>
+        <v>0.8182870370370371</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4771,29 +4771,29 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>svc_smote_splashing_ordenc</t>
+          <t>xgbclassifier_ohe_splashing</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E136" t="n">
-        <v>0.8659793814432989</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="F136" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G136" t="n">
-        <v>0.875</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H136" t="n">
-        <v>0.8078703703703703</v>
+        <v>0.8368055555555556</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4803,29 +4803,29 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>svc_splashing_ordenc</t>
+          <t>xgbclassifier_splashing</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.8</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E137" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="F137" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G137" t="n">
-        <v>0.9375</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H137" t="n">
-        <v>0.7465277777777777</v>
+        <v>0.8368055555555556</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4835,29 +4835,29 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_splashing_onehot</t>
+          <t>catboostclassifier_ohe_smote_splashing</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.84</v>
       </c>
       <c r="E138" t="n">
-        <v>0.8979591836734694</v>
+        <v>0.875</v>
       </c>
       <c r="F138" t="n">
-        <v>0.88</v>
+        <v>0.875</v>
       </c>
       <c r="G138" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="H138" t="n">
-        <v>0.8472222222222222</v>
+        <v>0.8263888888888888</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4867,29 +4867,29 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_splashing_onehot</t>
+          <t>catboostclassifier_smote_splashing</t>
         </is>
       </c>
       <c r="D139" t="n">
         <v>0.8533333333333334</v>
       </c>
       <c r="E139" t="n">
-        <v>0.8910891089108911</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="F139" t="n">
-        <v>0.8490566037735849</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G139" t="n">
-        <v>0.9375</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H139" t="n">
-        <v>0.8206018518518519</v>
+        <v>0.8368055555555556</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4899,29 +4899,29 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_splashing_ordenc</t>
+          <t>catboostclassifier_ohe_splashing</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.88</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="E140" t="n">
-        <v>0.9072164948453607</v>
+        <v>0.8686868686868686</v>
       </c>
       <c r="F140" t="n">
-        <v>0.8979591836734694</v>
+        <v>0.8431372549019608</v>
       </c>
       <c r="G140" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H140" t="n">
-        <v>0.8657407407407407</v>
+        <v>0.7997685185185186</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_splashing_ordenc</t>
+          <t>catboostclassifier_splashing</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -4953,135 +4953,135 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>xgbclassifier_smote_splashing</t>
+          <t>logisticregression_smote_net_impact_onehot</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.84</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E142" t="n">
-        <v>0.8799999999999999</v>
+        <v>0.7659574468085106</v>
       </c>
       <c r="F142" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G142" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9</v>
       </c>
       <c r="H142" t="n">
-        <v>0.8101851851851851</v>
+        <v>0.8681818181818182</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>xgbclassifier_splashing</t>
+          <t>logisticregression_net_impact_onehot</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="E143" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="F143" t="n">
-        <v>0.86</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G143" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="H143" t="n">
-        <v>0.8182870370370371</v>
+        <v>0.8545454545454545</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>catboostclassifier_smote_splashing</t>
+          <t>logisticregression_smote_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.84</v>
       </c>
       <c r="E144" t="n">
-        <v>0.8979591836734694</v>
+        <v>0.7391304347826088</v>
       </c>
       <c r="F144" t="n">
-        <v>0.88</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="G144" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.85</v>
       </c>
       <c r="H144" t="n">
-        <v>0.8472222222222222</v>
+        <v>0.8431818181818183</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>catboostclassifier_splashing</t>
+          <t>logisticregression_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E145" t="n">
-        <v>0.9</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="F145" t="n">
-        <v>0.8653846153846154</v>
+        <v>0.8</v>
       </c>
       <c r="G145" t="n">
-        <v>0.9375</v>
+        <v>0.8</v>
       </c>
       <c r="H145" t="n">
-        <v>0.8391203703703703</v>
+        <v>0.8636363636363636</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5091,29 +5091,29 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>logisticregression_smote_net_impact_onehot</t>
+          <t>svc_smote_net_impact_onehot</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E146" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.8260869565217392</v>
       </c>
       <c r="F146" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="G146" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H146" t="n">
-        <v>0.8681818181818182</v>
+        <v>0.9113636363636364</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5123,29 +5123,29 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>logisticregression_net_impact_onehot</t>
+          <t>svc_net_impact_onehot</t>
         </is>
       </c>
       <c r="D147" t="n">
         <v>0.88</v>
       </c>
       <c r="E147" t="n">
-        <v>0.7692307692307692</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="F147" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="G147" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H147" t="n">
-        <v>0.8386363636363635</v>
+        <v>0.8068181818181818</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5155,29 +5155,29 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>logisticregression_smote_net_impact_ordenc</t>
+          <t>svc_smote_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E148" t="n">
-        <v>0.7555555555555556</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="F148" t="n">
-        <v>0.68</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="G148" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H148" t="n">
-        <v>0.8522727272727272</v>
+        <v>0.8772727272727272</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5187,29 +5187,29 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>logisticregression_net_impact_ordenc</t>
+          <t>svc_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D149" t="n">
         <v>0.8933333333333333</v>
       </c>
       <c r="E149" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.7894736842105262</v>
       </c>
       <c r="F149" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G149" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="H149" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.8477272727272728</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5219,29 +5219,29 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>svc_smote_net_impact_onehot</t>
+          <t>kneighborsclassifier_smote_net_impact_onehot</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.88</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="E150" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.7659574468085106</v>
       </c>
       <c r="F150" t="n">
-        <v>0.72</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G150" t="n">
         <v>0.9</v>
       </c>
       <c r="H150" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.8681818181818182</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5251,29 +5251,29 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>svc_net_impact_onehot</t>
+          <t>kneighborsclassifier_net_impact_onehot</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.92</v>
       </c>
       <c r="E151" t="n">
-        <v>0.7222222222222223</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="F151" t="n">
-        <v>0.8125</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="G151" t="n">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="H151" t="n">
-        <v>0.7977272727272726</v>
+        <v>0.9136363636363636</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>svc_smote_net_impact_ordenc</t>
+          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5305,7 +5305,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5315,29 +5315,29 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>svc_net_impact_ordenc</t>
+          <t>kneighborsclassifier_net_impact_ordenc</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="E153" t="n">
-        <v>0.7368421052631577</v>
+        <v>0.8780487804878048</v>
       </c>
       <c r="F153" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G153" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="H153" t="n">
-        <v>0.8136363636363635</v>
+        <v>0.9227272727272726</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5347,29 +5347,29 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_net_impact_onehot</t>
+          <t>xgbclassifier_ohe_smote_net_impact</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="E154" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="F154" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.85</v>
       </c>
       <c r="G154" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H154" t="n">
-        <v>0.859090909090909</v>
+        <v>0.8977272727272728</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5379,29 +5379,29 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_net_impact_onehot</t>
+          <t>xgbclassifier_smote_net_impact</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0.88</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="E155" t="n">
-        <v>0.7906976744186046</v>
+        <v>0.8717948717948718</v>
       </c>
       <c r="F155" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="G155" t="n">
         <v>0.85</v>
       </c>
       <c r="H155" t="n">
-        <v>0.8704545454545455</v>
+        <v>0.9068181818181819</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5411,29 +5411,29 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
+          <t>xgbclassifier_ohe_net_impact</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E156" t="n">
-        <v>0.7826086956521738</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="F156" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.875</v>
       </c>
       <c r="G156" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="H156" t="n">
-        <v>0.8772727272727272</v>
+        <v>0.8318181818181818</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5443,29 +5443,29 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_net_impact_ordenc</t>
+          <t>xgbclassifier_net_impact</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0.88</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E157" t="n">
-        <v>0.7906976744186046</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="F157" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.875</v>
       </c>
       <c r="G157" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="H157" t="n">
-        <v>0.8704545454545455</v>
+        <v>0.8318181818181818</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5475,29 +5475,29 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>xgbclassifier_smote_net_impact</t>
+          <t>catboostclassifier_ohe_smote_net_impact</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.92</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="E158" t="n">
-        <v>0.8421052631578948</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="F158" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="G158" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="H158" t="n">
-        <v>0.8818181818181818</v>
+        <v>0.8795454545454546</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5507,29 +5507,29 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>xgbclassifier_net_impact</t>
+          <t>catboostclassifier_smote_net_impact</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="E159" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.8780487804878048</v>
       </c>
       <c r="F159" t="n">
-        <v>0.875</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G159" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="H159" t="n">
-        <v>0.8318181818181818</v>
+        <v>0.9227272727272726</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5539,29 +5539,29 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>catboostclassifier_smote_net_impact</t>
+          <t>catboostclassifier_ohe_net_impact</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.92</v>
       </c>
       <c r="E160" t="n">
-        <v>0.8372093023255814</v>
+        <v>0.85</v>
       </c>
       <c r="F160" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.85</v>
       </c>
       <c r="G160" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H160" t="n">
-        <v>0.9045454545454544</v>
+        <v>0.8977272727272728</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5575,19 +5575,1299 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="E161" t="n">
-        <v>0.9</v>
+        <v>0.8780487804878048</v>
       </c>
       <c r="F161" t="n">
-        <v>0.9</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G161" t="n">
         <v>0.9</v>
       </c>
       <c r="H161" t="n">
-        <v>0.9318181818181818</v>
+        <v>0.9227272727272726</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.845360824742268</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.8367346938775511</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.7789351851851851</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.8686868686868686</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.7997685185185186</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.7523148148148149</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0.8035714285714286</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.7650462962962963</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.851063829787234</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.8055555555555556</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>svc_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.7361111111111112</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.8723404255319149</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0.8913043478260869</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.8344907407407407</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>svc_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0.7962962962962963</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.744212962962963</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.8297872340425533</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0.8478260869565217</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.7766203703703703</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>0.7866666666666666</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.7685185185185186</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.795138888888889</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.845360824742268</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.8367346938775511</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.7789351851851851</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>xgbclassifier_ohe_smote_splashing</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0.8263888888888888</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>xgbclassifier_smote_splashing</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.9052631578947369</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.9148936170212766</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.8738425925925927</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>xgbclassifier_ohe_splashing</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.8865979381443299</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0.8368055555555556</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>xgbclassifier_splashing</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0.8865979381443299</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.8368055555555556</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>catboostclassifier_ohe_smote_splashing</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.8865979381443299</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0.8368055555555556</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>catboostclassifier_smote_splashing</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0.8553240740740742</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>catboostclassifier_ohe_splashing</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0.8686868686868686</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.7997685185185186</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>catboostclassifier_splashing</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0.8391203703703703</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.8681818181818182</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.8386363636363635</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.8613636363636364</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.8727272727272728</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.8863636363636364</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>svc_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.8068181818181818</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0.7826086956521738</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.8772727272727272</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>svc_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0.7058823529411764</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.7818181818181819</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.8681818181818182</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.9136363636363636</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0.8863636363636364</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0.9136363636363636</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>xgbclassifier_ohe_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0.9068181818181819</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>xgbclassifier_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0.8421052631578948</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0.8818181818181818</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>xgbclassifier_ohe_net_impact</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0.8318181818181818</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>xgbclassifier_net_impact</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0.8318181818181818</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>catboostclassifier_ohe_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0.9045454545454544</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>catboostclassifier_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0.9045454545454544</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>catboostclassifier_ohe_net_impact</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0.8977272727272728</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>catboostclassifier_net_impact</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0.8780487804878048</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0.9227272727272726</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_modelling2.xlsx
+++ b/results/metrics_modelling2.xlsx
@@ -9293,7 +9293,7 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>

--- a/results/metrics_modelling2.xlsx
+++ b/results/metrics_modelling2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J265"/>
+  <dimension ref="A1:J297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9326,7 +9326,7 @@
         <v>0.9409090909090908</v>
       </c>
       <c r="J234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -9364,7 +9364,7 @@
         <v>0.9409090909090908</v>
       </c>
       <c r="J235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -9402,7 +9402,7 @@
         <v>0.9386363636363636</v>
       </c>
       <c r="J236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -9440,7 +9440,7 @@
         <v>0.9159090909090909</v>
       </c>
       <c r="J237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -9478,7 +9478,7 @@
         <v>0.8795454545454546</v>
       </c>
       <c r="J238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -9516,7 +9516,7 @@
         <v>0.8545454545454545</v>
       </c>
       <c r="J239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -9554,7 +9554,7 @@
         <v>0.9318181818181818</v>
       </c>
       <c r="J240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -9592,7 +9592,7 @@
         <v>0.8795454545454546</v>
       </c>
       <c r="J241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -9630,7 +9630,7 @@
         <v>0.9068181818181819</v>
       </c>
       <c r="J242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -9668,7 +9668,7 @@
         <v>0.8727272727272728</v>
       </c>
       <c r="J243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -9706,7 +9706,7 @@
         <v>0.8727272727272728</v>
       </c>
       <c r="J244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -9744,7 +9744,7 @@
         <v>0.8727272727272728</v>
       </c>
       <c r="J245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -9782,7 +9782,7 @@
         <v>0.9159090909090909</v>
       </c>
       <c r="J246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -9820,7 +9820,7 @@
         <v>0.9068181818181819</v>
       </c>
       <c r="J247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -9858,7 +9858,7 @@
         <v>0.9068181818181819</v>
       </c>
       <c r="J248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -9896,7 +9896,7 @@
         <v>0.8738425925925927</v>
       </c>
       <c r="J249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -9934,7 +9934,7 @@
         <v>0.7835648148148149</v>
       </c>
       <c r="J250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -9972,7 +9972,7 @@
         <v>0.8738425925925927</v>
       </c>
       <c r="J251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -10010,7 +10010,7 @@
         <v>0.8842592592592592</v>
       </c>
       <c r="J252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -10048,7 +10048,7 @@
         <v>0.8657407407407407</v>
       </c>
       <c r="J253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -10086,7 +10086,7 @@
         <v>0.8946759259259259</v>
       </c>
       <c r="J254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -10124,7 +10124,7 @@
         <v>0.8946759259259259</v>
       </c>
       <c r="J255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -10162,7 +10162,7 @@
         <v>0.8946759259259259</v>
       </c>
       <c r="J256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -10200,7 +10200,7 @@
         <v>0.9050925925925927</v>
       </c>
       <c r="J257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -10238,7 +10238,7 @@
         <v>0.9050925925925927</v>
       </c>
       <c r="J258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -10276,7 +10276,7 @@
         <v>0.775462962962963</v>
       </c>
       <c r="J259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -10314,7 +10314,7 @@
         <v>0.8101851851851851</v>
       </c>
       <c r="J260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -10352,7 +10352,7 @@
         <v>0.9131944444444444</v>
       </c>
       <c r="J261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -10390,7 +10390,7 @@
         <v>0.9050925925925927</v>
       </c>
       <c r="J262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -10428,7 +10428,7 @@
         <v>0.8287037037037036</v>
       </c>
       <c r="J263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -10466,7 +10466,7 @@
         <v>0.8472222222222222</v>
       </c>
       <c r="J264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -10504,6 +10504,1222 @@
         <v>0.8182870370370371</v>
       </c>
       <c r="J265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>catboostclassifier_net_impact</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>0.9733333333333334</v>
+      </c>
+      <c r="F266" t="n">
+        <v>0.9473684210526316</v>
+      </c>
+      <c r="G266" t="n">
+        <v>1</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J266" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>265</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>catboostclassifier_net_impact</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F267" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0.9409090909090908</v>
+      </c>
+      <c r="J267" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>266</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>catboostclassifier_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0.8837209302325583</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0.9386363636363636</v>
+      </c>
+      <c r="J268" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>267</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>0.9466666666666667</v>
+      </c>
+      <c r="F269" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0.9159090909090909</v>
+      </c>
+      <c r="J269" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>xgbclassifier_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F270" t="n">
+        <v>0.7804878048780488</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I270" t="n">
+        <v>0.8545454545454545</v>
+      </c>
+      <c r="J270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>269</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>xgbclassifier_ohe_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0.7894736842105262</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I271" t="n">
+        <v>0.8477272727272728</v>
+      </c>
+      <c r="J271" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>0.9466666666666667</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H272" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I272" t="n">
+        <v>0.9318181818181818</v>
+      </c>
+      <c r="J272" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>271</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>xgbclassifier_ohe_smote_net_impact</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="H273" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I273" t="n">
+        <v>0.8704545454545455</v>
+      </c>
+      <c r="J273" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>272</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_onehot</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0.8780487804878048</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="H274" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I274" t="n">
+        <v>0.9227272727272726</v>
+      </c>
+      <c r="J274" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>273</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="H275" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I275" t="n">
+        <v>0.8727272727272728</v>
+      </c>
+      <c r="J275" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>274</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="H276" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I276" t="n">
+        <v>0.8727272727272728</v>
+      </c>
+      <c r="J276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n">
+        <v>275</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="H277" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I277" t="n">
+        <v>0.8727272727272728</v>
+      </c>
+      <c r="J277" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n">
+        <v>276</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>0.9466666666666667</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="G278" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="H278" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I278" t="n">
+        <v>0.9159090909090909</v>
+      </c>
+      <c r="J278" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n">
+        <v>277</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0.8780487804878048</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="H279" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I279" t="n">
+        <v>0.9227272727272726</v>
+      </c>
+      <c r="J279" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n">
+        <v>278</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_ordenc</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="H280" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I280" t="n">
+        <v>0.9068181818181819</v>
+      </c>
+      <c r="J280" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n">
+        <v>279</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0.9052631578947369</v>
+      </c>
+      <c r="G281" t="n">
+        <v>0.9148936170212766</v>
+      </c>
+      <c r="H281" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="I281" t="n">
+        <v>0.8738425925925927</v>
+      </c>
+      <c r="J281" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>xgbclassifier_smote_splashing</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F282" t="n">
+        <v>0.8737864077669902</v>
+      </c>
+      <c r="G282" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="H282" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="I282" t="n">
+        <v>0.7835648148148149</v>
+      </c>
+      <c r="J282" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="n">
+        <v>281</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0.9052631578947369</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0.9148936170212766</v>
+      </c>
+      <c r="H283" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="I283" t="n">
+        <v>0.8738425925925927</v>
+      </c>
+      <c r="J283" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="n">
+        <v>282</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>catboostclassifier_smote_splashing</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0.9263157894736843</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0.9361702127659575</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="I284" t="n">
+        <v>0.9027777777777777</v>
+      </c>
+      <c r="J284" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>283</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0.9052631578947369</v>
+      </c>
+      <c r="G285" t="n">
+        <v>0.9148936170212766</v>
+      </c>
+      <c r="H285" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="I285" t="n">
+        <v>0.8738425925925927</v>
+      </c>
+      <c r="J285" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="n">
+        <v>284</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>catboostclassifier_smote_splashing</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F286" t="n">
+        <v>0.9278350515463918</v>
+      </c>
+      <c r="G286" t="n">
+        <v>0.9183673469387755</v>
+      </c>
+      <c r="H286" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="I286" t="n">
+        <v>0.8946759259259259</v>
+      </c>
+      <c r="J286" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="n">
+        <v>285</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>catboostclassifier_splashing</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0.9278350515463918</v>
+      </c>
+      <c r="G287" t="n">
+        <v>0.9183673469387755</v>
+      </c>
+      <c r="H287" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="I287" t="n">
+        <v>0.8946759259259259</v>
+      </c>
+      <c r="J287" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="n">
+        <v>286</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>catboostclassifier_splashing</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F288" t="n">
+        <v>0.9278350515463918</v>
+      </c>
+      <c r="G288" t="n">
+        <v>0.9183673469387755</v>
+      </c>
+      <c r="H288" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0.8946759259259259</v>
+      </c>
+      <c r="J288" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>287</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F289" t="n">
+        <v>0.9387755102040817</v>
+      </c>
+      <c r="G289" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H289" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="I289" t="n">
+        <v>0.9050925925925927</v>
+      </c>
+      <c r="J289" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>288</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F290" t="n">
+        <v>0.9387755102040817</v>
+      </c>
+      <c r="G290" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H290" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="I290" t="n">
+        <v>0.9050925925925927</v>
+      </c>
+      <c r="J290" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>289</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>xgbclassifier_ohe_smote_splashing</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>0.8266666666666667</v>
+      </c>
+      <c r="F291" t="n">
+        <v>0.8737864077669902</v>
+      </c>
+      <c r="G291" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="H291" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="I291" t="n">
+        <v>0.7835648148148149</v>
+      </c>
+      <c r="J291" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>290</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F292" t="n">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="G292" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="H292" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="I292" t="n">
+        <v>0.8101851851851851</v>
+      </c>
+      <c r="J292" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>291</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="H293" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="I293" t="n">
+        <v>0.9131944444444444</v>
+      </c>
+      <c r="J293" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>292</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_ordenc</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0.9387755102040817</v>
+      </c>
+      <c r="G294" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H294" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="I294" t="n">
+        <v>0.9050925925925927</v>
+      </c>
+      <c r="J294" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>293</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F295" t="n">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="G295" t="n">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="H295" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="I295" t="n">
+        <v>0.8287037037037036</v>
+      </c>
+      <c r="J295" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>294</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F296" t="n">
+        <v>0.8842105263157894</v>
+      </c>
+      <c r="G296" t="n">
+        <v>0.8936170212765957</v>
+      </c>
+      <c r="H296" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I296" t="n">
+        <v>0.8449074074074074</v>
+      </c>
+      <c r="J296" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="n">
+        <v>295</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_onehot</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F297" t="n">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="G297" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="H297" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="I297" t="n">
+        <v>0.8101851851851851</v>
+      </c>
+      <c r="J297" t="n">
         <v>1</v>
       </c>
     </row>

--- a/results/metrics_modelling2.xlsx
+++ b/results/metrics_modelling2.xlsx
@@ -425,10 +425,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J297"/>
+  <dimension ref="A1:J321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>dataset</t>
@@ -476,7 +481,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -514,7 +519,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -552,7 +557,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -590,7 +595,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -628,7 +633,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -666,7 +671,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -704,7 +709,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -742,7 +747,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -780,7 +785,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -818,7 +823,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -856,7 +861,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -932,7 +937,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -970,7 +975,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1008,7 +1013,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1046,7 +1051,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1084,7 +1089,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1122,7 +1127,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1160,7 +1165,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1198,7 +1203,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1236,7 +1241,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1274,7 +1279,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1312,7 +1317,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1350,7 +1355,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1388,7 +1393,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1426,7 +1431,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1464,7 +1469,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1502,7 +1507,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1540,7 +1545,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1578,7 +1583,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1616,7 +1621,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1654,7 +1659,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1692,7 +1697,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1730,7 +1735,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>33</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1768,7 +1773,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1806,7 +1811,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>35</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1844,7 +1849,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>36</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -1882,7 +1887,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>37</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -1920,7 +1925,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>38</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -1958,7 +1963,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>39</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -1996,7 +2001,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>40</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2034,7 +2039,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>41</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2072,7 +2077,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>42</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2110,7 +2115,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>43</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2148,7 +2153,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>44</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2186,7 +2191,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" t="n">
         <v>45</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -2224,7 +2229,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" t="n">
         <v>46</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2262,7 +2267,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" t="n">
         <v>47</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2300,7 +2305,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" t="n">
         <v>48</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2338,7 +2343,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" t="n">
         <v>49</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2376,7 +2381,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" t="n">
         <v>50</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2414,7 +2419,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" t="n">
         <v>51</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2452,7 +2457,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" t="n">
         <v>52</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -2490,7 +2495,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" t="n">
         <v>53</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -2528,7 +2533,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" t="n">
         <v>54</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -2566,7 +2571,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" t="n">
         <v>55</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2604,7 +2609,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" t="n">
         <v>56</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2642,7 +2647,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" t="n">
         <v>57</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2680,7 +2685,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" t="n">
         <v>58</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -2718,7 +2723,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" t="n">
         <v>59</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -2756,7 +2761,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" t="n">
         <v>60</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2794,7 +2799,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" t="n">
         <v>61</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -2832,7 +2837,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" t="n">
         <v>62</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2870,7 +2875,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" t="n">
         <v>63</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -2908,7 +2913,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" t="n">
         <v>64</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -2946,7 +2951,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" t="n">
         <v>65</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -2984,7 +2989,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" t="n">
         <v>66</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -3022,7 +3027,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" t="n">
         <v>67</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -3060,7 +3065,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" t="n">
         <v>68</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -3098,7 +3103,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" t="n">
         <v>69</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -3136,7 +3141,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" t="n">
         <v>70</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -3174,7 +3179,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" t="n">
         <v>71</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -3212,7 +3217,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" t="n">
         <v>72</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -3250,7 +3255,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" t="n">
         <v>73</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -3288,7 +3293,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" t="n">
         <v>74</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -3326,7 +3331,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" t="n">
         <v>75</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -3364,7 +3369,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" t="n">
         <v>76</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -3402,7 +3407,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" t="n">
         <v>77</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3440,7 +3445,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" t="n">
         <v>78</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -3478,7 +3483,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" t="n">
         <v>79</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -3516,7 +3521,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" t="n">
         <v>80</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -3554,7 +3559,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" t="n">
         <v>81</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -3592,7 +3597,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" t="n">
         <v>82</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -3630,7 +3635,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" t="n">
         <v>83</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -3668,7 +3673,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" t="n">
         <v>84</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -3706,7 +3711,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" t="n">
         <v>85</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -3744,7 +3749,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" t="n">
         <v>86</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -3782,7 +3787,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" t="n">
         <v>87</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -3820,7 +3825,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" t="n">
         <v>88</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -3858,7 +3863,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" t="n">
         <v>89</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -3896,7 +3901,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" t="n">
         <v>90</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -3934,7 +3939,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" t="n">
         <v>91</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -3972,7 +3977,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" t="n">
         <v>92</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -4010,7 +4015,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" t="n">
         <v>93</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -4048,7 +4053,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" t="n">
         <v>94</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -4086,7 +4091,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" t="n">
         <v>95</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -4124,7 +4129,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" t="n">
         <v>96</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -4162,7 +4167,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" t="n">
         <v>97</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -4200,7 +4205,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" t="n">
         <v>98</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -4238,7 +4243,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" t="n">
         <v>99</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -4276,7 +4281,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" t="n">
         <v>100</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -4314,7 +4319,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" t="n">
         <v>101</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -4352,7 +4357,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" t="n">
         <v>102</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -4390,7 +4395,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" t="n">
         <v>103</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -4428,7 +4433,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" t="n">
         <v>104</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -4466,7 +4471,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" t="n">
         <v>105</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -4504,7 +4509,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" t="n">
         <v>106</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -4542,7 +4547,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" t="n">
         <v>107</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -4580,7 +4585,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" t="n">
         <v>108</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -4618,7 +4623,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" t="n">
         <v>109</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -4656,7 +4661,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" t="n">
         <v>110</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -4694,7 +4699,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" t="n">
         <v>111</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -4732,7 +4737,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" t="n">
         <v>112</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -4770,7 +4775,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" t="n">
         <v>113</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -4808,7 +4813,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" t="n">
         <v>114</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -4846,7 +4851,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" t="n">
         <v>115</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -4884,7 +4889,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" t="n">
         <v>116</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -4922,7 +4927,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" t="n">
         <v>117</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -4960,7 +4965,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" t="n">
         <v>118</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -4998,7 +5003,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" t="n">
         <v>119</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -5036,7 +5041,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" t="n">
         <v>120</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -5074,7 +5079,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" t="n">
         <v>121</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -5112,7 +5117,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" t="n">
         <v>122</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -5150,7 +5155,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" t="n">
         <v>123</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -5188,7 +5193,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" t="n">
         <v>124</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -5226,7 +5231,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" t="n">
         <v>125</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -5264,7 +5269,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" t="n">
         <v>126</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -5302,7 +5307,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" t="n">
         <v>127</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -5340,7 +5345,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" t="n">
         <v>128</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -5378,7 +5383,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" t="n">
         <v>129</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -5416,7 +5421,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" t="n">
         <v>130</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -5454,7 +5459,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" t="n">
         <v>131</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -5492,7 +5497,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" t="n">
         <v>132</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -5530,7 +5535,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" t="n">
         <v>133</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -5568,7 +5573,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" t="n">
         <v>134</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -5606,7 +5611,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" t="n">
         <v>135</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -5644,7 +5649,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" t="n">
         <v>136</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -5682,7 +5687,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" t="n">
         <v>137</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -5720,7 +5725,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" t="n">
         <v>138</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -5758,7 +5763,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" t="n">
         <v>139</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -5796,7 +5801,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" t="n">
         <v>140</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -5834,7 +5839,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" t="n">
         <v>141</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -5872,7 +5877,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" t="n">
         <v>142</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -5910,7 +5915,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" t="n">
         <v>143</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -5948,7 +5953,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" t="n">
         <v>144</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -5986,7 +5991,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" t="n">
         <v>145</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -6024,7 +6029,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" t="n">
         <v>146</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -6062,7 +6067,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" t="n">
         <v>147</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -6100,7 +6105,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" t="n">
         <v>148</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -6138,7 +6143,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" t="n">
         <v>149</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -6176,7 +6181,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" t="n">
         <v>150</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -6214,7 +6219,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" t="n">
         <v>151</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -6252,7 +6257,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" t="n">
         <v>152</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -6290,7 +6295,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" t="n">
         <v>153</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -6328,7 +6333,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" t="n">
         <v>154</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -6366,7 +6371,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" t="n">
         <v>155</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -6404,7 +6409,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" t="n">
         <v>156</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -6442,7 +6447,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" t="n">
         <v>157</v>
       </c>
       <c r="B159" t="inlineStr">
@@ -6480,7 +6485,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" t="n">
         <v>158</v>
       </c>
       <c r="B160" t="inlineStr">
@@ -6518,7 +6523,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" t="n">
         <v>159</v>
       </c>
       <c r="B161" t="inlineStr">
@@ -6556,7 +6561,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" t="n">
         <v>160</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -6594,7 +6599,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" t="n">
         <v>161</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -6632,7 +6637,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" t="n">
         <v>162</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -6670,7 +6675,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" t="n">
         <v>163</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -6708,7 +6713,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" t="n">
         <v>164</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -6746,7 +6751,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" t="n">
         <v>165</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -6784,7 +6789,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" t="n">
         <v>166</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -6822,7 +6827,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" t="n">
         <v>167</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -6860,7 +6865,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" t="n">
         <v>168</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -6898,7 +6903,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" t="n">
         <v>169</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -6936,7 +6941,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" t="n">
         <v>170</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -6974,7 +6979,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" t="n">
         <v>171</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -7012,7 +7017,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" t="n">
         <v>172</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -7050,7 +7055,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" t="n">
         <v>173</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -7088,7 +7093,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" t="n">
         <v>174</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -7126,7 +7131,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" t="n">
         <v>175</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -7164,7 +7169,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" t="n">
         <v>176</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -7202,7 +7207,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" t="n">
         <v>177</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -7240,7 +7245,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" t="n">
         <v>178</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -7278,7 +7283,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" t="n">
         <v>179</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -7316,7 +7321,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" t="n">
         <v>180</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -7354,7 +7359,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" t="n">
         <v>181</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -7392,7 +7397,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" t="n">
         <v>182</v>
       </c>
       <c r="B184" t="inlineStr">
@@ -7430,7 +7435,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" t="n">
         <v>183</v>
       </c>
       <c r="B185" t="inlineStr">
@@ -7468,7 +7473,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" t="n">
         <v>184</v>
       </c>
       <c r="B186" t="inlineStr">
@@ -7506,7 +7511,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" t="n">
         <v>185</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -7544,7 +7549,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" t="n">
         <v>186</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -7582,7 +7587,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" t="n">
         <v>187</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -7620,7 +7625,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" t="n">
         <v>188</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -7658,7 +7663,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" t="n">
         <v>189</v>
       </c>
       <c r="B191" t="inlineStr">
@@ -7696,7 +7701,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" t="n">
         <v>190</v>
       </c>
       <c r="B192" t="inlineStr">
@@ -7734,7 +7739,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" t="n">
         <v>191</v>
       </c>
       <c r="B193" t="inlineStr">
@@ -7772,7 +7777,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" t="n">
         <v>192</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -7810,7 +7815,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" t="n">
         <v>193</v>
       </c>
       <c r="B195" t="inlineStr">
@@ -7848,7 +7853,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" t="n">
         <v>194</v>
       </c>
       <c r="B196" t="inlineStr">
@@ -7886,7 +7891,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" t="n">
         <v>195</v>
       </c>
       <c r="B197" t="inlineStr">
@@ -7924,7 +7929,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" t="n">
         <v>196</v>
       </c>
       <c r="B198" t="inlineStr">
@@ -7962,7 +7967,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" t="n">
         <v>197</v>
       </c>
       <c r="B199" t="inlineStr">
@@ -8000,7 +8005,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" t="n">
         <v>198</v>
       </c>
       <c r="B200" t="inlineStr">
@@ -8038,7 +8043,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" t="n">
         <v>199</v>
       </c>
       <c r="B201" t="inlineStr">
@@ -8076,7 +8081,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" t="n">
         <v>200</v>
       </c>
       <c r="B202" t="inlineStr">
@@ -8114,7 +8119,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" t="n">
         <v>201</v>
       </c>
       <c r="B203" t="inlineStr">
@@ -8152,7 +8157,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" t="n">
         <v>202</v>
       </c>
       <c r="B204" t="inlineStr">
@@ -8190,7 +8195,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" t="n">
         <v>203</v>
       </c>
       <c r="B205" t="inlineStr">
@@ -8228,7 +8233,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" t="n">
         <v>204</v>
       </c>
       <c r="B206" t="inlineStr">
@@ -8266,7 +8271,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" t="n">
         <v>205</v>
       </c>
       <c r="B207" t="inlineStr">
@@ -8304,7 +8309,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" t="n">
         <v>206</v>
       </c>
       <c r="B208" t="inlineStr">
@@ -8342,7 +8347,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" t="n">
         <v>207</v>
       </c>
       <c r="B209" t="inlineStr">
@@ -8380,7 +8385,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" t="n">
         <v>208</v>
       </c>
       <c r="B210" t="inlineStr">
@@ -8418,7 +8423,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" t="n">
         <v>209</v>
       </c>
       <c r="B211" t="inlineStr">
@@ -8456,7 +8461,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" t="n">
         <v>210</v>
       </c>
       <c r="B212" t="inlineStr">
@@ -8494,7 +8499,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" t="n">
         <v>211</v>
       </c>
       <c r="B213" t="inlineStr">
@@ -8532,7 +8537,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" t="n">
         <v>212</v>
       </c>
       <c r="B214" t="inlineStr">
@@ -8570,7 +8575,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" t="n">
         <v>213</v>
       </c>
       <c r="B215" t="inlineStr">
@@ -8608,7 +8613,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" t="n">
         <v>214</v>
       </c>
       <c r="B216" t="inlineStr">
@@ -8646,7 +8651,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" t="n">
         <v>215</v>
       </c>
       <c r="B217" t="inlineStr">
@@ -8684,7 +8689,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" t="n">
         <v>216</v>
       </c>
       <c r="B218" t="inlineStr">
@@ -8722,7 +8727,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" t="n">
         <v>217</v>
       </c>
       <c r="B219" t="inlineStr">
@@ -8760,7 +8765,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" t="n">
         <v>218</v>
       </c>
       <c r="B220" t="inlineStr">
@@ -8798,7 +8803,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" t="n">
         <v>219</v>
       </c>
       <c r="B221" t="inlineStr">
@@ -8836,7 +8841,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" t="n">
         <v>220</v>
       </c>
       <c r="B222" t="inlineStr">
@@ -8874,7 +8879,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" t="n">
         <v>221</v>
       </c>
       <c r="B223" t="inlineStr">
@@ -8912,7 +8917,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" t="n">
         <v>222</v>
       </c>
       <c r="B224" t="inlineStr">
@@ -8950,7 +8955,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" t="n">
         <v>223</v>
       </c>
       <c r="B225" t="inlineStr">
@@ -8988,7 +8993,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" t="n">
         <v>224</v>
       </c>
       <c r="B226" t="inlineStr">
@@ -9026,7 +9031,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" t="n">
         <v>225</v>
       </c>
       <c r="B227" t="inlineStr">
@@ -9064,7 +9069,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" t="n">
         <v>226</v>
       </c>
       <c r="B228" t="inlineStr">
@@ -9102,7 +9107,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" t="n">
         <v>227</v>
       </c>
       <c r="B229" t="inlineStr">
@@ -9140,7 +9145,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" t="n">
         <v>228</v>
       </c>
       <c r="B230" t="inlineStr">
@@ -9178,7 +9183,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" t="n">
         <v>229</v>
       </c>
       <c r="B231" t="inlineStr">
@@ -9216,7 +9221,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" t="n">
         <v>230</v>
       </c>
       <c r="B232" t="inlineStr">
@@ -9254,7 +9259,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" t="n">
         <v>231</v>
       </c>
       <c r="B233" t="inlineStr">
@@ -9292,7 +9297,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" t="n">
         <v>232</v>
       </c>
       <c r="B234" t="inlineStr">
@@ -9330,7 +9335,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" t="n">
         <v>233</v>
       </c>
       <c r="B235" t="inlineStr">
@@ -9368,7 +9373,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" t="n">
         <v>234</v>
       </c>
       <c r="B236" t="inlineStr">
@@ -9406,7 +9411,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" t="n">
         <v>235</v>
       </c>
       <c r="B237" t="inlineStr">
@@ -9444,7 +9449,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" t="n">
         <v>236</v>
       </c>
       <c r="B238" t="inlineStr">
@@ -9482,7 +9487,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" t="n">
         <v>237</v>
       </c>
       <c r="B239" t="inlineStr">
@@ -9520,7 +9525,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" t="n">
         <v>238</v>
       </c>
       <c r="B240" t="inlineStr">
@@ -9558,7 +9563,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" t="n">
         <v>239</v>
       </c>
       <c r="B241" t="inlineStr">
@@ -9596,7 +9601,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" t="n">
         <v>240</v>
       </c>
       <c r="B242" t="inlineStr">
@@ -9634,7 +9639,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" t="n">
         <v>241</v>
       </c>
       <c r="B243" t="inlineStr">
@@ -9672,7 +9677,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" t="n">
         <v>242</v>
       </c>
       <c r="B244" t="inlineStr">
@@ -9710,7 +9715,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" t="n">
         <v>243</v>
       </c>
       <c r="B245" t="inlineStr">
@@ -9748,7 +9753,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" t="n">
         <v>244</v>
       </c>
       <c r="B246" t="inlineStr">
@@ -9786,7 +9791,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" t="n">
         <v>245</v>
       </c>
       <c r="B247" t="inlineStr">
@@ -9824,7 +9829,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" t="n">
         <v>246</v>
       </c>
       <c r="B248" t="inlineStr">
@@ -9862,7 +9867,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" t="n">
         <v>247</v>
       </c>
       <c r="B249" t="inlineStr">
@@ -9900,7 +9905,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" t="n">
         <v>248</v>
       </c>
       <c r="B250" t="inlineStr">
@@ -9938,7 +9943,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" t="n">
         <v>249</v>
       </c>
       <c r="B251" t="inlineStr">
@@ -9976,7 +9981,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" t="n">
         <v>250</v>
       </c>
       <c r="B252" t="inlineStr">
@@ -10014,7 +10019,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" t="n">
         <v>251</v>
       </c>
       <c r="B253" t="inlineStr">
@@ -10052,7 +10057,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" t="n">
         <v>252</v>
       </c>
       <c r="B254" t="inlineStr">
@@ -10090,7 +10095,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" t="n">
         <v>253</v>
       </c>
       <c r="B255" t="inlineStr">
@@ -10128,7 +10133,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" t="n">
         <v>254</v>
       </c>
       <c r="B256" t="inlineStr">
@@ -10166,7 +10171,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" t="n">
         <v>255</v>
       </c>
       <c r="B257" t="inlineStr">
@@ -10204,7 +10209,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" t="n">
         <v>256</v>
       </c>
       <c r="B258" t="inlineStr">
@@ -10242,7 +10247,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" t="n">
         <v>257</v>
       </c>
       <c r="B259" t="inlineStr">
@@ -10280,7 +10285,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" t="n">
         <v>258</v>
       </c>
       <c r="B260" t="inlineStr">
@@ -10318,7 +10323,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" t="n">
         <v>259</v>
       </c>
       <c r="B261" t="inlineStr">
@@ -10356,7 +10361,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" t="n">
         <v>260</v>
       </c>
       <c r="B262" t="inlineStr">
@@ -10394,7 +10399,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" t="n">
         <v>261</v>
       </c>
       <c r="B263" t="inlineStr">
@@ -10432,7 +10437,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" t="n">
         <v>262</v>
       </c>
       <c r="B264" t="inlineStr">
@@ -10470,7 +10475,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" t="n">
         <v>263</v>
       </c>
       <c r="B265" t="inlineStr">
@@ -10508,7 +10513,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" t="n">
         <v>264</v>
       </c>
       <c r="B266" t="inlineStr">
@@ -10546,7 +10551,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" t="n">
         <v>265</v>
       </c>
       <c r="B267" t="inlineStr">
@@ -10584,7 +10589,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" t="n">
         <v>266</v>
       </c>
       <c r="B268" t="inlineStr">
@@ -10622,7 +10627,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" t="n">
         <v>267</v>
       </c>
       <c r="B269" t="inlineStr">
@@ -10660,7 +10665,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" t="n">
         <v>268</v>
       </c>
       <c r="B270" t="inlineStr">
@@ -10698,7 +10703,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" t="n">
         <v>269</v>
       </c>
       <c r="B271" t="inlineStr">
@@ -10736,7 +10741,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" t="n">
         <v>270</v>
       </c>
       <c r="B272" t="inlineStr">
@@ -10774,7 +10779,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" t="n">
         <v>271</v>
       </c>
       <c r="B273" t="inlineStr">
@@ -10812,7 +10817,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" t="n">
         <v>272</v>
       </c>
       <c r="B274" t="inlineStr">
@@ -10850,7 +10855,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" t="n">
         <v>273</v>
       </c>
       <c r="B275" t="inlineStr">
@@ -10888,7 +10893,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" t="n">
         <v>274</v>
       </c>
       <c r="B276" t="inlineStr">
@@ -10926,7 +10931,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" t="n">
         <v>275</v>
       </c>
       <c r="B277" t="inlineStr">
@@ -10964,7 +10969,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" t="n">
         <v>276</v>
       </c>
       <c r="B278" t="inlineStr">
@@ -11002,7 +11007,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" t="n">
         <v>277</v>
       </c>
       <c r="B279" t="inlineStr">
@@ -11040,7 +11045,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" t="n">
         <v>278</v>
       </c>
       <c r="B280" t="inlineStr">
@@ -11078,7 +11083,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" t="n">
         <v>279</v>
       </c>
       <c r="B281" t="inlineStr">
@@ -11116,7 +11121,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" t="n">
         <v>280</v>
       </c>
       <c r="B282" t="inlineStr">
@@ -11154,7 +11159,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" t="n">
         <v>281</v>
       </c>
       <c r="B283" t="inlineStr">
@@ -11192,7 +11197,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" t="n">
         <v>282</v>
       </c>
       <c r="B284" t="inlineStr">
@@ -11230,7 +11235,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" t="n">
         <v>283</v>
       </c>
       <c r="B285" t="inlineStr">
@@ -11268,7 +11273,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" t="n">
         <v>284</v>
       </c>
       <c r="B286" t="inlineStr">
@@ -11306,7 +11311,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" t="n">
         <v>285</v>
       </c>
       <c r="B287" t="inlineStr">
@@ -11344,7 +11349,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" t="n">
         <v>286</v>
       </c>
       <c r="B288" t="inlineStr">
@@ -11382,7 +11387,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" t="n">
         <v>287</v>
       </c>
       <c r="B289" t="inlineStr">
@@ -11420,7 +11425,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" t="n">
         <v>288</v>
       </c>
       <c r="B290" t="inlineStr">
@@ -11458,7 +11463,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" t="n">
         <v>289</v>
       </c>
       <c r="B291" t="inlineStr">
@@ -11496,7 +11501,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" t="n">
         <v>290</v>
       </c>
       <c r="B292" t="inlineStr">
@@ -11534,7 +11539,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" t="n">
         <v>291</v>
       </c>
       <c r="B293" t="inlineStr">
@@ -11572,7 +11577,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" t="n">
         <v>292</v>
       </c>
       <c r="B294" t="inlineStr">
@@ -11610,7 +11615,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" t="n">
         <v>293</v>
       </c>
       <c r="B295" t="inlineStr">
@@ -11648,7 +11653,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" t="n">
         <v>294</v>
       </c>
       <c r="B296" t="inlineStr">
@@ -11686,7 +11691,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" t="n">
         <v>295</v>
       </c>
       <c r="B297" t="inlineStr">
@@ -11722,6 +11727,822 @@
       <c r="J297" t="n">
         <v>1</v>
       </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr"/>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_splashing_binary_onehot</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F298" t="n">
+        <v>0.8085106382978724</v>
+      </c>
+      <c r="G298" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="H298" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="I298" t="n">
+        <v>0.7476851851851851</v>
+      </c>
+      <c r="J298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr"/>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_binary_onehot</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0.8349514563106797</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0.7818181818181819</v>
+      </c>
+      <c r="H299" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="I299" t="n">
+        <v>0.7256944444444445</v>
+      </c>
+      <c r="J299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr"/>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_splashing_binary_ordenc</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="F300" t="n">
+        <v>0.7872340425531915</v>
+      </c>
+      <c r="G300" t="n">
+        <v>0.8043478260869565</v>
+      </c>
+      <c r="H300" t="n">
+        <v>0.7708333333333334</v>
+      </c>
+      <c r="I300" t="n">
+        <v>0.7187500000000001</v>
+      </c>
+      <c r="J300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr"/>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>logisticregression_splashing_binary_ordenc</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="F301" t="n">
+        <v>0.838095238095238</v>
+      </c>
+      <c r="G301" t="n">
+        <v>0.7719298245614035</v>
+      </c>
+      <c r="H301" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="I301" t="n">
+        <v>0.7175925925925926</v>
+      </c>
+      <c r="J301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr"/>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_binary_onehot</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F302" t="n">
+        <v>0.8799999999999999</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="H302" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="I302" t="n">
+        <v>0.8101851851851851</v>
+      </c>
+      <c r="J302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr"/>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>svc_splashing_binary_onehot</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F303" t="n">
+        <v>0.8679245283018867</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="H303" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="I303" t="n">
+        <v>0.7569444444444444</v>
+      </c>
+      <c r="J303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr"/>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_binary_ordenc</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F304" t="n">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="G304" t="n">
+        <v>0.8627450980392157</v>
+      </c>
+      <c r="H304" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="I304" t="n">
+        <v>0.8287037037037036</v>
+      </c>
+      <c r="J304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>svc_splashing_binary_ordenc</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F305" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="G305" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="H305" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="I305" t="n">
+        <v>0.7465277777777777</v>
+      </c>
+      <c r="J305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_splashing_binary_onehot</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="F306" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="G306" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="H306" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="I306" t="n">
+        <v>0.7974537037037036</v>
+      </c>
+      <c r="J306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr"/>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_splashing_binary_onehot</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F307" t="n">
+        <v>0.8910891089108911</v>
+      </c>
+      <c r="G307" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="H307" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="I307" t="n">
+        <v>0.8206018518518519</v>
+      </c>
+      <c r="J307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_splashing_binary_ordenc</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F308" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G308" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H308" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I308" t="n">
+        <v>0.8263888888888888</v>
+      </c>
+      <c r="J308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr"/>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_splashing_binary_ordenc</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F309" t="n">
+        <v>0.8910891089108911</v>
+      </c>
+      <c r="G309" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="I309" t="n">
+        <v>0.8206018518518519</v>
+      </c>
+      <c r="J309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr"/>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_net_impact_binary_onehot</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F310" t="n">
+        <v>0.7659574468085106</v>
+      </c>
+      <c r="G310" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H310" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I310" t="n">
+        <v>0.8681818181818182</v>
+      </c>
+      <c r="J310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr"/>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_binary_onehot</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="F311" t="n">
+        <v>0.7894736842105262</v>
+      </c>
+      <c r="G311" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="H311" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I311" t="n">
+        <v>0.8477272727272728</v>
+      </c>
+      <c r="J311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr"/>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>logisticregression_smote_net_impact_binary_ordenc</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F312" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="G312" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="H312" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I312" t="n">
+        <v>0.8613636363636364</v>
+      </c>
+      <c r="J312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr"/>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>logisticregression_net_impact_binary_ordenc</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F313" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="G313" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="H313" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I313" t="n">
+        <v>0.8386363636363635</v>
+      </c>
+      <c r="J313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr"/>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_binary_onehot</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F314" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="G314" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="H314" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I314" t="n">
+        <v>0.9045454545454544</v>
+      </c>
+      <c r="J314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr"/>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>svc_net_impact_binary_onehot</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F315" t="n">
+        <v>0.7222222222222223</v>
+      </c>
+      <c r="G315" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H315" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I315" t="n">
+        <v>0.7977272727272726</v>
+      </c>
+      <c r="J315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr"/>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_binary_ordenc</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F316" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="G316" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="H316" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I316" t="n">
+        <v>0.9045454545454544</v>
+      </c>
+      <c r="J316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr"/>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>svc_net_impact_binary_ordenc</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F317" t="n">
+        <v>0.7368421052631577</v>
+      </c>
+      <c r="G317" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="H317" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I317" t="n">
+        <v>0.8136363636363635</v>
+      </c>
+      <c r="J317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr"/>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_net_impact_binary_onehot</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F318" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="G318" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I318" t="n">
+        <v>0.8613636363636364</v>
+      </c>
+      <c r="J318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr"/>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_net_impact_binary_onehot</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F319" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="G319" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="H319" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I319" t="n">
+        <v>0.8386363636363635</v>
+      </c>
+      <c r="J319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr"/>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_smote_net_impact_binary_ordenc</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="F320" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="G320" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="H320" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I320" t="n">
+        <v>0.8795454545454546</v>
+      </c>
+      <c r="J320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr"/>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>kneighborsclassifier_net_impact_binary_ordenc</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>0.9066666666666666</v>
+      </c>
+      <c r="F321" t="n">
+        <v>0.8108108108108107</v>
+      </c>
+      <c r="G321" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="H321" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I321" t="n">
+        <v>0.8568181818181818</v>
+      </c>
+      <c r="J321" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
